--- a/Data Files/Auto/RecusaPropostaAuto/RecusaPropostasAuto.xlsx
+++ b/Data Files/Auto/RecusaPropostaAuto/RecusaPropostasAuto.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Auto\RecusaPropostaAuto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{22E443A4-947B-49BC-8D5B-FCB7BDD39956}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1442B8-8183-400E-BD81-BFDEAA960502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
-    <sheet name="RecusaPropostaAuto" r:id="rId1" sheetId="1"/>
+    <sheet name="RecusaPropostaAuto" sheetId="1" r:id="rId1"/>
+    <sheet name="18.07.24" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">RecusaPropostaAuto!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaPropostaAuto!$A$1:$C$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="214">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -42,230 +43,640 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>119781702</t>
-  </si>
-  <si>
-    <t>119845151</t>
-  </si>
-  <si>
-    <t>119929143</t>
-  </si>
-  <si>
-    <t>119989356</t>
-  </si>
-  <si>
-    <t>120218359</t>
-  </si>
-  <si>
-    <t>120281256</t>
-  </si>
-  <si>
-    <t>120559974</t>
-  </si>
-  <si>
-    <t>121369966</t>
-  </si>
-  <si>
-    <t>121595996</t>
-  </si>
-  <si>
-    <t>121696316</t>
-  </si>
-  <si>
-    <t>122126825</t>
-  </si>
-  <si>
-    <t>122399911</t>
-  </si>
-  <si>
-    <t>122952653</t>
-  </si>
-  <si>
-    <t>123122484</t>
-  </si>
-  <si>
-    <t>123123202</t>
-  </si>
-  <si>
-    <t>123123504</t>
-  </si>
-  <si>
-    <t>123124086</t>
-  </si>
-  <si>
-    <t>123124370</t>
-  </si>
-  <si>
-    <t>123124613</t>
-  </si>
-  <si>
-    <t>123124759</t>
-  </si>
-  <si>
-    <t>123125165</t>
-  </si>
-  <si>
-    <t>123125494</t>
-  </si>
-  <si>
-    <t>123125779</t>
-  </si>
-  <si>
-    <t>123126038</t>
-  </si>
-  <si>
-    <t>123126253</t>
-  </si>
-  <si>
-    <t>123127256</t>
-  </si>
-  <si>
-    <t>123127916</t>
-  </si>
-  <si>
-    <t>123128085</t>
-  </si>
-  <si>
-    <t>123128239</t>
-  </si>
-  <si>
-    <t>123128342</t>
-  </si>
-  <si>
-    <t>123128448</t>
-  </si>
-  <si>
-    <t>123128653</t>
-  </si>
-  <si>
-    <t>123129018</t>
-  </si>
-  <si>
-    <t>123129023</t>
-  </si>
-  <si>
-    <t>123129134</t>
-  </si>
-  <si>
-    <t>123129353</t>
-  </si>
-  <si>
-    <t>123129847</t>
-  </si>
-  <si>
-    <t>123129891</t>
-  </si>
-  <si>
-    <t>123130033</t>
-  </si>
-  <si>
-    <t>123130074</t>
-  </si>
-  <si>
-    <t>123130197</t>
-  </si>
-  <si>
-    <t>123130384</t>
-  </si>
-  <si>
-    <t>123130426</t>
-  </si>
-  <si>
-    <t>123130596</t>
-  </si>
-  <si>
-    <t>123130872</t>
-  </si>
-  <si>
-    <t>123130906</t>
-  </si>
-  <si>
-    <t>123131293</t>
-  </si>
-  <si>
-    <t>123132450</t>
-  </si>
-  <si>
-    <t>123132595</t>
-  </si>
-  <si>
-    <t>123132908</t>
-  </si>
-  <si>
-    <t>123132976</t>
-  </si>
-  <si>
-    <t>123133078</t>
-  </si>
-  <si>
-    <t>123133177</t>
-  </si>
-  <si>
-    <t>123133289</t>
-  </si>
-  <si>
-    <t>123133584</t>
-  </si>
-  <si>
-    <t>123133801</t>
-  </si>
-  <si>
-    <t>123134040</t>
-  </si>
-  <si>
-    <t>123134114</t>
-  </si>
-  <si>
-    <t>123134148</t>
-  </si>
-  <si>
-    <t>123134204</t>
-  </si>
-  <si>
-    <t>123134224</t>
-  </si>
-  <si>
-    <t>123134310</t>
-  </si>
-  <si>
-    <t>123134451</t>
-  </si>
-  <si>
-    <t>123134723</t>
-  </si>
-  <si>
-    <t>123134786</t>
-  </si>
-  <si>
-    <t>123135104</t>
-  </si>
-  <si>
-    <t>123135331</t>
-  </si>
-  <si>
-    <t>123135357</t>
-  </si>
-  <si>
-    <t>123136036</t>
-  </si>
-  <si>
-    <t>123136039</t>
-  </si>
-  <si>
-    <t>123136179</t>
-  </si>
-  <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>119781702/0/2 2023-03-22 at 22:49:34 BRT</t>
+    <t>.</t>
+  </si>
+  <si>
+    <t>125280880</t>
+  </si>
+  <si>
+    <t>125312567</t>
+  </si>
+  <si>
+    <t>125686662</t>
+  </si>
+  <si>
+    <t>125839741</t>
+  </si>
+  <si>
+    <t>126413124</t>
+  </si>
+  <si>
+    <t>126672635</t>
+  </si>
+  <si>
+    <t>126768997</t>
+  </si>
+  <si>
+    <t>126931761</t>
+  </si>
+  <si>
+    <t>127258004</t>
+  </si>
+  <si>
+    <t>127381520</t>
+  </si>
+  <si>
+    <t>127453862</t>
+  </si>
+  <si>
+    <t>127549399</t>
+  </si>
+  <si>
+    <t>127741603</t>
+  </si>
+  <si>
+    <t>127757939</t>
+  </si>
+  <si>
+    <t>128183585</t>
+  </si>
+  <si>
+    <t>128381036</t>
+  </si>
+  <si>
+    <t>128381290</t>
+  </si>
+  <si>
+    <t>128381417</t>
+  </si>
+  <si>
+    <t>128381424</t>
+  </si>
+  <si>
+    <t>128381548</t>
+  </si>
+  <si>
+    <t>128381579</t>
+  </si>
+  <si>
+    <t>128381681</t>
+  </si>
+  <si>
+    <t>128381725</t>
+  </si>
+  <si>
+    <t>128381881</t>
+  </si>
+  <si>
+    <t>128382051</t>
+  </si>
+  <si>
+    <t>128382261</t>
+  </si>
+  <si>
+    <t>128382691</t>
+  </si>
+  <si>
+    <t>128382808</t>
+  </si>
+  <si>
+    <t>128382989</t>
+  </si>
+  <si>
+    <t>128383203</t>
+  </si>
+  <si>
+    <t>128383313</t>
+  </si>
+  <si>
+    <t>128383376</t>
+  </si>
+  <si>
+    <t>128383425</t>
+  </si>
+  <si>
+    <t>128383794</t>
+  </si>
+  <si>
+    <t>128383837</t>
+  </si>
+  <si>
+    <t>128383996</t>
+  </si>
+  <si>
+    <t>128384093</t>
+  </si>
+  <si>
+    <t>128384148</t>
+  </si>
+  <si>
+    <t>128384277</t>
+  </si>
+  <si>
+    <t>128384282</t>
+  </si>
+  <si>
+    <t>128384685</t>
+  </si>
+  <si>
+    <t>128384851</t>
+  </si>
+  <si>
+    <t>128384877</t>
+  </si>
+  <si>
+    <t>128385021</t>
+  </si>
+  <si>
+    <t>128385161</t>
+  </si>
+  <si>
+    <t>128385441</t>
+  </si>
+  <si>
+    <t>128385494</t>
+  </si>
+  <si>
+    <t>128385513</t>
+  </si>
+  <si>
+    <t>128385587</t>
+  </si>
+  <si>
+    <t>128385695</t>
+  </si>
+  <si>
+    <t>128385774</t>
+  </si>
+  <si>
+    <t>128385909</t>
+  </si>
+  <si>
+    <t>128386183</t>
+  </si>
+  <si>
+    <t>128386335</t>
+  </si>
+  <si>
+    <t>128386398</t>
+  </si>
+  <si>
+    <t>128386418</t>
+  </si>
+  <si>
+    <t>128386430</t>
+  </si>
+  <si>
+    <t>128386477</t>
+  </si>
+  <si>
+    <t>128386501</t>
+  </si>
+  <si>
+    <t>128386581</t>
+  </si>
+  <si>
+    <t>128386628</t>
+  </si>
+  <si>
+    <t>128386646</t>
+  </si>
+  <si>
+    <t>128386823</t>
+  </si>
+  <si>
+    <t>128386887</t>
+  </si>
+  <si>
+    <t>128386999</t>
+  </si>
+  <si>
+    <t>128387064</t>
+  </si>
+  <si>
+    <t>128387075</t>
+  </si>
+  <si>
+    <t>128387157</t>
+  </si>
+  <si>
+    <t>128387262</t>
+  </si>
+  <si>
+    <t>128387336</t>
+  </si>
+  <si>
+    <t>128387460</t>
+  </si>
+  <si>
+    <t>128387642</t>
+  </si>
+  <si>
+    <t>128387837</t>
+  </si>
+  <si>
+    <t>128387839</t>
+  </si>
+  <si>
+    <t>128387936</t>
+  </si>
+  <si>
+    <t>128387991</t>
+  </si>
+  <si>
+    <t>128388014</t>
+  </si>
+  <si>
+    <t>128388048</t>
+  </si>
+  <si>
+    <t>128388064</t>
+  </si>
+  <si>
+    <t>128388114</t>
+  </si>
+  <si>
+    <t>128388424</t>
+  </si>
+  <si>
+    <t>128388440</t>
+  </si>
+  <si>
+    <t>128388814</t>
+  </si>
+  <si>
+    <t>128388820</t>
+  </si>
+  <si>
+    <t>128388841</t>
+  </si>
+  <si>
+    <t>128388946</t>
+  </si>
+  <si>
+    <t>128389052</t>
+  </si>
+  <si>
+    <t>128389616</t>
+  </si>
+  <si>
+    <t>128389624</t>
+  </si>
+  <si>
+    <t>128389836</t>
+  </si>
+  <si>
+    <t>128389879</t>
+  </si>
+  <si>
+    <t>128390049</t>
+  </si>
+  <si>
+    <t>128390111</t>
+  </si>
+  <si>
+    <t>128390240</t>
+  </si>
+  <si>
+    <t>128390282</t>
+  </si>
+  <si>
+    <t>128390321</t>
+  </si>
+  <si>
+    <t>128390464</t>
+  </si>
+  <si>
+    <t>128390763</t>
+  </si>
+  <si>
+    <t>128390819</t>
+  </si>
+  <si>
+    <t>128391010</t>
+  </si>
+  <si>
+    <t>128391077</t>
+  </si>
+  <si>
+    <t>128391135</t>
+  </si>
+  <si>
+    <t>128391145</t>
+  </si>
+  <si>
+    <t>128391171</t>
+  </si>
+  <si>
+    <t>128391511</t>
+  </si>
+  <si>
+    <t>128391602</t>
+  </si>
+  <si>
+    <t>128391663</t>
+  </si>
+  <si>
+    <t>128391873</t>
+  </si>
+  <si>
+    <t>128392128</t>
+  </si>
+  <si>
+    <t>128392340</t>
+  </si>
+  <si>
+    <t>128392341</t>
+  </si>
+  <si>
+    <t>128392379</t>
+  </si>
+  <si>
+    <t>128392494</t>
+  </si>
+  <si>
+    <t>128392597</t>
+  </si>
+  <si>
+    <t>128392985</t>
+  </si>
+  <si>
+    <t>128393043</t>
+  </si>
+  <si>
+    <t>128393197</t>
+  </si>
+  <si>
+    <t>128393245</t>
+  </si>
+  <si>
+    <t>128393317</t>
+  </si>
+  <si>
+    <t>128393758</t>
+  </si>
+  <si>
+    <t>128393992</t>
+  </si>
+  <si>
+    <t>128394095</t>
+  </si>
+  <si>
+    <t>128394134</t>
+  </si>
+  <si>
+    <t>128394197</t>
+  </si>
+  <si>
+    <t>128394314</t>
+  </si>
+  <si>
+    <t>128394333</t>
+  </si>
+  <si>
+    <t>128394363</t>
+  </si>
+  <si>
+    <t>128394398</t>
+  </si>
+  <si>
+    <t>128394526</t>
+  </si>
+  <si>
+    <t>128394630</t>
+  </si>
+  <si>
+    <t>128394635</t>
+  </si>
+  <si>
+    <t>128394710</t>
+  </si>
+  <si>
+    <t>128394737</t>
+  </si>
+  <si>
+    <t>128394879</t>
+  </si>
+  <si>
+    <t>128394931</t>
+  </si>
+  <si>
+    <t>128394967</t>
+  </si>
+  <si>
+    <t>128395016</t>
+  </si>
+  <si>
+    <t>128395105</t>
+  </si>
+  <si>
+    <t>128395444</t>
+  </si>
+  <si>
+    <t>128395742</t>
+  </si>
+  <si>
+    <t>128395769</t>
+  </si>
+  <si>
+    <t>128395799</t>
+  </si>
+  <si>
+    <t>128395898</t>
+  </si>
+  <si>
+    <t>128396008</t>
+  </si>
+  <si>
+    <t>128396156</t>
+  </si>
+  <si>
+    <t>128396177</t>
+  </si>
+  <si>
+    <t>128396185</t>
+  </si>
+  <si>
+    <t>128396219</t>
+  </si>
+  <si>
+    <t>128396244</t>
+  </si>
+  <si>
+    <t>128396303</t>
+  </si>
+  <si>
+    <t>128396490</t>
+  </si>
+  <si>
+    <t>128396506</t>
+  </si>
+  <si>
+    <t>128396583</t>
+  </si>
+  <si>
+    <t>128396649</t>
+  </si>
+  <si>
+    <t>128396673</t>
+  </si>
+  <si>
+    <t>128396800</t>
+  </si>
+  <si>
+    <t>128396805</t>
+  </si>
+  <si>
+    <t>128396811</t>
+  </si>
+  <si>
+    <t>128397067</t>
+  </si>
+  <si>
+    <t>128397075</t>
+  </si>
+  <si>
+    <t>128397090</t>
+  </si>
+  <si>
+    <t>128397268</t>
+  </si>
+  <si>
+    <t>128397426</t>
+  </si>
+  <si>
+    <t>128397462</t>
+  </si>
+  <si>
+    <t>128397464</t>
+  </si>
+  <si>
+    <t>128397469</t>
+  </si>
+  <si>
+    <t>128397522</t>
+  </si>
+  <si>
+    <t>128397531</t>
+  </si>
+  <si>
+    <t>128397606</t>
+  </si>
+  <si>
+    <t>128397661</t>
+  </si>
+  <si>
+    <t>128397715</t>
+  </si>
+  <si>
+    <t>128397865</t>
+  </si>
+  <si>
+    <t>128397923</t>
+  </si>
+  <si>
+    <t>128398100</t>
+  </si>
+  <si>
+    <t>128398109</t>
+  </si>
+  <si>
+    <t>128398183</t>
+  </si>
+  <si>
+    <t>128398453</t>
+  </si>
+  <si>
+    <t>128398618</t>
+  </si>
+  <si>
+    <t>128398738</t>
+  </si>
+  <si>
+    <t>128398787</t>
+  </si>
+  <si>
+    <t>128398841</t>
+  </si>
+  <si>
+    <t>128399012</t>
+  </si>
+  <si>
+    <t>128399023</t>
+  </si>
+  <si>
+    <t>128399031</t>
+  </si>
+  <si>
+    <t>128399108</t>
+  </si>
+  <si>
+    <t>128399238</t>
+  </si>
+  <si>
+    <t>128399347</t>
+  </si>
+  <si>
+    <t>128399376</t>
+  </si>
+  <si>
+    <t>128399401</t>
+  </si>
+  <si>
+    <t>128399411</t>
+  </si>
+  <si>
+    <t>128399517</t>
+  </si>
+  <si>
+    <t>128399518</t>
+  </si>
+  <si>
+    <t>128399533</t>
+  </si>
+  <si>
+    <t>128399597</t>
+  </si>
+  <si>
+    <t>128399641</t>
+  </si>
+  <si>
+    <t>128399720</t>
+  </si>
+  <si>
+    <t>128399744</t>
+  </si>
+  <si>
+    <t>128400065</t>
+  </si>
+  <si>
+    <t>128400140</t>
+  </si>
+  <si>
+    <t>128400141</t>
+  </si>
+  <si>
+    <t>128400430</t>
+  </si>
+  <si>
+    <t>128400609</t>
+  </si>
+  <si>
+    <t>128400631</t>
+  </si>
+  <si>
+    <t>128401839</t>
+  </si>
+  <si>
+    <t>128402003</t>
+  </si>
+  <si>
+    <t>128402141</t>
+  </si>
+  <si>
+    <t>128402206</t>
+  </si>
+  <si>
+    <t>128402224</t>
+  </si>
+  <si>
+    <t>128402229</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -334,31 +745,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="1" numFmtId="49" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="1" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyNumberFormat="1" borderId="0" fillId="4" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -375,10 +789,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -413,7 +827,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -465,7 +879,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -576,21 +990,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -607,7 +1021,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -659,21 +1073,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:D72"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
+  <dimension ref="A1:C215"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="3" width="14.42578125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="3" width="11.5703125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="3" width="81.7109375" collapsed="true"/>
-    <col min="4" max="16384" style="3" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="14.42578125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="11.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="81.7109375" style="3" customWidth="1" collapsed="1"/>
+    <col min="4" max="16384" width="9.140625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -688,649 +1102,2372 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
+      <c r="A2" s="6">
+        <v>124636793</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
+      <c r="A3" s="6">
+        <v>124721964</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
+      <c r="A4" s="6">
+        <v>124920078</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
+      <c r="A5" s="6">
+        <v>125142441</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
+      <c r="A6" s="6">
+        <v>125204528</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="C11" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="5"/>
+      <c r="C17" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="5"/>
+      <c r="C22" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="5"/>
+      <c r="C23" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="5"/>
+      <c r="C25" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="5"/>
+      <c r="C27" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="5"/>
+      <c r="C28" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="5"/>
+      <c r="C29" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="5"/>
+      <c r="C30" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="5"/>
+      <c r="C31" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="5"/>
+      <c r="C32" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="5"/>
+      <c r="C33" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="5"/>
+      <c r="C34" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="5"/>
+      <c r="C35" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="5"/>
+      <c r="C36" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="5"/>
+      <c r="C37" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="5"/>
+      <c r="C38" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="5"/>
+      <c r="C39" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="5"/>
+      <c r="C40" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="5"/>
+      <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="5"/>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C43" s="5"/>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C44" s="5"/>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C45" s="5"/>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="5"/>
+      <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="5"/>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C48" s="5"/>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C49" s="5"/>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C50" s="5"/>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="5"/>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="5"/>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="5"/>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C54" s="5"/>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C55" s="5"/>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C56" s="5"/>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C57" s="5"/>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="5"/>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C59" s="5"/>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C60" s="5"/>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C61" s="5"/>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="5"/>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C63" s="5"/>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C64" s="5"/>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C65" s="5"/>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C66" s="5"/>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C67" s="5"/>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C68" s="5"/>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C69" s="5"/>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="5"/>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="5"/>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C72" s="5"/>
+      <c r="B76" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C9" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <autoFilter ref="A1:C6" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{060D8E49-4039-47DD-B5AF-00B702E82C23}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>